--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-observation-radiology-impression.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-observation-radiology-impression.xlsx
@@ -1030,7 +1030,7 @@
     <t>配偶者、親、胎児、ドナーなど、このObservationのsubject要素が実際の対象でない場合、その実際の対象に関する情報</t>
   </si>
   <si>
-    <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
+    <t>通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1575,7 +1575,7 @@
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
   </si>
   <si>
-    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではない）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
